--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -811,6 +811,11 @@
           <t>はらや MAZE SOBA</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>⚠️ 過去にも入力あり (2回)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="44" t="n">
@@ -1996,10 +2001,25 @@
       <c r="A132" s="44" t="n">
         <v>46279</v>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>はらや MAZE SOBA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>⚠️ 過去にも入力あり (2回)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="44" t="n">
         <v>46280</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>はれる屋食堂</t>
+        </is>
       </c>
     </row>
     <row r="134">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2026,20 +2026,40 @@
       <c r="A134" s="44" t="n">
         <v>46281</v>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>七輪呑家 里估 – RICO –</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="44" t="n">
         <v>46282</v>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>abeille アベイユ</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="44" t="n">
         <v>46283</v>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>三河屋製菓</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="44" t="n">
         <v>46284</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>張闖麻辣燙</t>
+        </is>
       </c>
     </row>
     <row r="138">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2071,30 +2071,60 @@
       <c r="A139" s="44" t="n">
         <v>46286</v>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>京菓子所 亀忠菓舗</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="44" t="n">
         <v>46287</v>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>洋食cottolico(コトリコ)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="44" t="n">
         <v>46288</v>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EREBOS FITNESS GYM</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="44" t="n">
         <v>46289</v>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>センドハピネス</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="44" t="n">
         <v>46290</v>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>精文館書店 豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="44" t="n">
         <v>46291</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>abeille chiffoncake</t>
+        </is>
       </c>
     </row>
     <row r="145">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2136,30 +2136,70 @@
       <c r="A146" s="44" t="n">
         <v>46293</v>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CoCo壱</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="44" t="n">
         <v>46294</v>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>肉笑家</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="44" t="n">
         <v>46295</v>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ミソウソツカナイ豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="44" t="n">
         <v>46296</v>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>夕やけ横丁三丁目 豊川駅前店</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="44" t="n">
         <v>46297</v>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>大東園</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="44" t="n">
         <v>46298</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>セカンドストリート</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
       </c>
     </row>
     <row r="152">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2211,30 +2211,60 @@
       <c r="A153" s="44" t="n">
         <v>46300</v>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lumiere by Eir-LUXE</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="44" t="n">
         <v>46301</v>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CAFE＆GOLF LAUGHRAD</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="44" t="n">
         <v>46302</v>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ロビン・フッド</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="44" t="n">
         <v>46303</v>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>車検のコバック 豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="44" t="n">
         <v>46304</v>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>古着屋リバ村</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="44" t="n">
         <v>46305</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>LimAlign プリオ豊川店</t>
+        </is>
       </c>
     </row>
     <row r="159">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2276,30 +2276,60 @@
       <c r="A160" s="44" t="n">
         <v>46307</v>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SAN PHAM VIET</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="44" t="n">
         <v>46308</v>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>弁当 空（Sora）</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="44" t="n">
         <v>46309</v>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cream D</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="44" t="n">
         <v>46310</v>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Po CAFE（ポカフェ）</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="44" t="n">
         <v>46311</v>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Balloon &amp; Plants SHOP　BLOOM</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="44" t="n">
         <v>46312</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ちょい飲み あっちゃん家</t>
+        </is>
       </c>
     </row>
     <row r="166">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2341,30 +2341,60 @@
       <c r="A167" s="44" t="n">
         <v>46314</v>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>コバックカーズ 豊川インター店</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="44" t="n">
         <v>46315</v>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ナチュラルカフェ はつね</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="44" t="n">
         <v>46316</v>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>カフェはぴふる</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="44" t="n">
         <v>46317</v>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CROW men’ salon 豊川</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="44" t="n">
         <v>46318</v>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>餃子の店 北留</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="44" t="n">
         <v>46319</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>カネイチ農園「ミニトマト直売所」</t>
+        </is>
       </c>
     </row>
     <row r="173">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -2406,30 +2406,70 @@
       <c r="A174" s="44" t="n">
         <v>46321</v>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>フィットネスジム「LifeFit」</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="44" t="n">
         <v>46322</v>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>エッグノッグ</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="44" t="n">
         <v>46323</v>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>晩酌屋かわむら</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="44" t="n">
         <v>46324</v>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ACAI DAYS</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="44" t="n">
         <v>46325</v>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>クスリのアオキ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="44" t="n">
         <v>46326</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>コバックカーズ豊川インター店</t>
+        </is>
       </c>
     </row>
     <row r="180">
